--- a/news_daily/2026-08-10.xlsx
+++ b/news_daily/2026-08-10.xlsx
@@ -888,28 +888,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -953,7 +957,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -962,7 +966,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>640664c71a2c4cbd8812ea66675eaab3</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>ed684a819e1c8b5380a79127</t>
@@ -983,7 +991,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1027,10 +1039,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1081,13 +1105,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1140,7 +1168,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>460153bcce2146c8900f2111a9a01c9e</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>a909faf4c6f677b23be38a5e</t>
@@ -1161,7 +1193,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1199,8 +1235,16 @@
       <c r="BH3" s="2" t="inlineStr"/>
       <c r="BI3" s="2" t="inlineStr"/>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1236,28 +1280,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1301,7 +1349,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1310,7 +1358,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>b1c951e249f54ee8a85971655684d7ed</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>4df16ba554860dd118c51c8a</t>
@@ -1331,7 +1383,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1367,10 +1423,22 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2399,13 +2467,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2458,7 +2530,11 @@
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>061e0ad857d041a28dab27f5c4b10546</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>4399ee610beba5d846ef3b43</t>
@@ -2479,7 +2555,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -2525,8 +2605,16 @@
       <c r="BH10" s="2" t="inlineStr"/>
       <c r="BI10" s="2" t="inlineStr"/>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2562,28 +2650,32 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2627,7 +2719,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -2636,7 +2728,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>bea1bee0104d4f1b908cf7401881efe8</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>ca43ba60fcb711e08d5afc41</t>
@@ -2657,7 +2753,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2701,10 +2801,22 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
-      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2740,28 +2852,32 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2805,7 +2921,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -2814,7 +2930,11 @@
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>9bbeb317a3a44287947cfafa893c26bf</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>532e5d8b59ff0806a002763a</t>
@@ -2835,7 +2955,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -2871,10 +2995,22 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3512,28 +3648,32 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3577,7 +3717,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -3586,7 +3726,11 @@
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>f8f7b013f29c44fb841fb0de4bf66c4b</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>c0302bb77f4d4102e2aa326c</t>
@@ -3607,7 +3751,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3651,10 +3799,22 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
-      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3705,13 +3865,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3764,7 +3928,11 @@
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>a588e859101f4c81b9c706fa06b96681</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>42272734be3facb410838c7b</t>
@@ -3785,7 +3953,11 @@
       <c r="AL17" s="2" t="inlineStr"/>
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="2" t="inlineStr"/>
       <c r="AQ17" s="2" t="inlineStr"/>
       <c r="AR17" s="2" t="inlineStr"/>
@@ -3823,8 +3995,16 @@
       <c r="BH17" s="2" t="inlineStr"/>
       <c r="BI17" s="2" t="inlineStr"/>
       <c r="BJ17" s="2" t="inlineStr"/>
-      <c r="BK17" s="2" t="inlineStr"/>
-      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3875,13 +4055,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3934,7 +4118,11 @@
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>7eeb4159d96849339c2dd241c685725d</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>a9bab531f7ef3e35224c5b82</t>
@@ -3955,7 +4143,11 @@
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
@@ -4001,8 +4193,16 @@
       <c r="BH18" s="2" t="inlineStr"/>
       <c r="BI18" s="2" t="inlineStr"/>
       <c r="BJ18" s="2" t="inlineStr"/>
-      <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -4228,28 +4428,32 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4293,7 +4497,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -4302,7 +4506,11 @@
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>e49e0ebf66e74e13a2630e0fb11c5f5c</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>1961d0f5387296910d269e14</t>
@@ -4323,7 +4531,11 @@
       <c r="AL20" s="2" t="inlineStr"/>
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr"/>
-      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="2" t="inlineStr"/>
       <c r="AQ20" s="2" t="inlineStr"/>
       <c r="AR20" s="2" t="inlineStr"/>
@@ -4359,10 +4571,22 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
-      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="2" t="inlineStr"/>
-      <c r="BK20" s="2" t="inlineStr"/>
-      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4398,28 +4622,32 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4463,7 +4691,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -4472,7 +4700,11 @@
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>31a5dc65b87f45cda68a9fc822996c74</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>3e5e2e9e4cca753c04b69a22</t>
@@ -4493,7 +4725,11 @@
       <c r="AL21" s="2" t="inlineStr"/>
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr"/>
-      <c r="AO21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="2" t="inlineStr"/>
       <c r="AQ21" s="2" t="inlineStr"/>
       <c r="AR21" s="2" t="inlineStr"/>
@@ -4529,10 +4765,22 @@
         </is>
       </c>
       <c r="BH21" s="2" t="inlineStr"/>
-      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ21" s="2" t="inlineStr"/>
-      <c r="BK21" s="2" t="inlineStr"/>
-      <c r="BL21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4568,28 +4816,32 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4633,7 +4885,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -4642,7 +4894,11 @@
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>30cf3c0651444eeea14f2168bdd2adac</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>9669541aa0eaaed0104786f0</t>
@@ -4663,7 +4919,11 @@
       <c r="AL22" s="2" t="inlineStr"/>
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr"/>
-      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="2" t="inlineStr"/>
       <c r="AQ22" s="2" t="inlineStr"/>
       <c r="AR22" s="2" t="inlineStr"/>
@@ -4707,10 +4967,22 @@
         </is>
       </c>
       <c r="BH22" s="2" t="inlineStr"/>
-      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ22" s="2" t="inlineStr"/>
-      <c r="BK22" s="2" t="inlineStr"/>
-      <c r="BL22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4746,28 +5018,32 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4811,7 +5087,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -4820,7 +5096,11 @@
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr"/>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>484b6a4a08534f1790ba8a3ff2ea4e90</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>6bb34b8b6f557a3c169f8782</t>
@@ -4841,7 +5121,11 @@
       <c r="AL23" s="2" t="inlineStr"/>
       <c r="AM23" s="2" t="inlineStr"/>
       <c r="AN23" s="2" t="inlineStr"/>
-      <c r="AO23" s="2" t="inlineStr"/>
+      <c r="AO23" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP23" s="2" t="inlineStr"/>
       <c r="AQ23" s="2" t="inlineStr"/>
       <c r="AR23" s="2" t="inlineStr"/>
@@ -4885,10 +5169,22 @@
         </is>
       </c>
       <c r="BH23" s="2" t="inlineStr"/>
-      <c r="BI23" s="2" t="inlineStr"/>
+      <c r="BI23" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ23" s="2" t="inlineStr"/>
-      <c r="BK23" s="2" t="inlineStr"/>
-      <c r="BL23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5510,28 +5806,32 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -5575,7 +5875,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -5584,7 +5884,11 @@
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr"/>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>5243256090dd4688a8014bc76a64d32a</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
           <t>47acd893f7528f245b15d6e7</t>
@@ -5605,7 +5909,11 @@
       <c r="AL27" s="2" t="inlineStr"/>
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr"/>
-      <c r="AO27" s="2" t="inlineStr"/>
+      <c r="AO27" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP27" s="2" t="inlineStr"/>
       <c r="AQ27" s="2" t="inlineStr"/>
       <c r="AR27" s="2" t="inlineStr"/>
@@ -5641,10 +5949,22 @@
         </is>
       </c>
       <c r="BH27" s="2" t="inlineStr"/>
-      <c r="BI27" s="2" t="inlineStr"/>
+      <c r="BI27" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ27" s="2" t="inlineStr"/>
-      <c r="BK27" s="2" t="inlineStr"/>
-      <c r="BL27" s="2" t="inlineStr"/>
+      <c r="BK27" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6099,13 +6419,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -6158,7 +6482,11 @@
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr"/>
-      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>7e6f80afb2dc48deb453d8ffd0445a0a</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>174cbeec0cd99292aae45cff</t>
@@ -6179,7 +6507,11 @@
       <c r="AL30" s="2" t="inlineStr"/>
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr"/>
-      <c r="AO30" s="2" t="inlineStr"/>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP30" s="2" t="inlineStr"/>
       <c r="AQ30" s="2" t="inlineStr"/>
       <c r="AR30" s="2" t="inlineStr"/>
@@ -6225,8 +6557,16 @@
       <c r="BH30" s="2" t="inlineStr"/>
       <c r="BI30" s="2" t="inlineStr"/>
       <c r="BJ30" s="2" t="inlineStr"/>
-      <c r="BK30" s="2" t="inlineStr"/>
-      <c r="BL30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6262,28 +6602,32 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6327,7 +6671,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -6336,7 +6680,11 @@
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr"/>
-      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>8fcbb3fdda1a46ceaf202e1a10819e01</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
           <t>0bdde52c5dbfe62ccfad9a05</t>
@@ -6357,7 +6705,11 @@
       <c r="AL31" s="2" t="inlineStr"/>
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr"/>
-      <c r="AO31" s="2" t="inlineStr"/>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP31" s="2" t="inlineStr"/>
       <c r="AQ31" s="2" t="inlineStr"/>
       <c r="AR31" s="2" t="inlineStr"/>
@@ -6401,10 +6753,22 @@
         </is>
       </c>
       <c r="BH31" s="2" t="inlineStr"/>
-      <c r="BI31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ31" s="2" t="inlineStr"/>
-      <c r="BK31" s="2" t="inlineStr"/>
-      <c r="BL31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6657,13 +7021,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -6716,7 +7084,11 @@
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr"/>
-      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>35d8037322184b63931a7960ca1784d4</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
           <t>4c75b8fa1da8ecfd469c22bc</t>
@@ -6737,7 +7109,11 @@
       <c r="AL33" s="2" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr"/>
       <c r="AN33" s="2" t="inlineStr"/>
-      <c r="AO33" s="2" t="inlineStr"/>
+      <c r="AO33" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP33" s="2" t="inlineStr"/>
       <c r="AQ33" s="2" t="inlineStr"/>
       <c r="AR33" s="2" t="inlineStr"/>
@@ -6783,8 +7159,16 @@
       <c r="BH33" s="2" t="inlineStr"/>
       <c r="BI33" s="2" t="inlineStr"/>
       <c r="BJ33" s="2" t="inlineStr"/>
-      <c r="BK33" s="2" t="inlineStr"/>
-      <c r="BL33" s="2" t="inlineStr"/>
+      <c r="BK33" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6820,28 +7204,32 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6885,7 +7273,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -6894,7 +7282,11 @@
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr"/>
-      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>8f04e34a13cd43829781aac8cbafa2eb</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>41bf50681aa50e28b68d420b</t>
@@ -6915,7 +7307,11 @@
       <c r="AL34" s="2" t="inlineStr"/>
       <c r="AM34" s="2" t="inlineStr"/>
       <c r="AN34" s="2" t="inlineStr"/>
-      <c r="AO34" s="2" t="inlineStr"/>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP34" s="2" t="inlineStr"/>
       <c r="AQ34" s="2" t="inlineStr"/>
       <c r="AR34" s="2" t="inlineStr"/>
@@ -6951,10 +7347,22 @@
         </is>
       </c>
       <c r="BH34" s="2" t="inlineStr"/>
-      <c r="BI34" s="2" t="inlineStr"/>
+      <c r="BI34" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ34" s="2" t="inlineStr"/>
-      <c r="BK34" s="2" t="inlineStr"/>
-      <c r="BL34" s="2" t="inlineStr"/>
+      <c r="BK34" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6990,28 +7398,32 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -7055,7 +7467,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -7064,7 +7476,11 @@
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr"/>
-      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>f868e6bc1a594d498321347447ba5775</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
           <t>7c42c43795117b88a57f21ec</t>
@@ -7085,7 +7501,11 @@
       <c r="AL35" s="2" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr"/>
       <c r="AN35" s="2" t="inlineStr"/>
-      <c r="AO35" s="2" t="inlineStr"/>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP35" s="2" t="inlineStr"/>
       <c r="AQ35" s="2" t="inlineStr"/>
       <c r="AR35" s="2" t="inlineStr"/>
@@ -7129,10 +7549,22 @@
         </is>
       </c>
       <c r="BH35" s="2" t="inlineStr"/>
-      <c r="BI35" s="2" t="inlineStr"/>
+      <c r="BI35" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ35" s="2" t="inlineStr"/>
-      <c r="BK35" s="2" t="inlineStr"/>
-      <c r="BL35" s="2" t="inlineStr"/>
+      <c r="BK35" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -7358,28 +7790,32 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -7423,7 +7859,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -7432,7 +7868,11 @@
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr"/>
-      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>87e5c6f5d42a49c8ab41f60e03da1a6d</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
           <t>fd42891969a47925e545313f</t>
@@ -7453,7 +7893,11 @@
       <c r="AL37" s="2" t="inlineStr"/>
       <c r="AM37" s="2" t="inlineStr"/>
       <c r="AN37" s="2" t="inlineStr"/>
-      <c r="AO37" s="2" t="inlineStr"/>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP37" s="2" t="inlineStr"/>
       <c r="AQ37" s="2" t="inlineStr"/>
       <c r="AR37" s="2" t="inlineStr"/>
@@ -7497,10 +7941,22 @@
         </is>
       </c>
       <c r="BH37" s="2" t="inlineStr"/>
-      <c r="BI37" s="2" t="inlineStr"/>
+      <c r="BI37" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ37" s="2" t="inlineStr"/>
-      <c r="BK37" s="2" t="inlineStr"/>
-      <c r="BL37" s="2" t="inlineStr"/>
+      <c r="BK37" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7551,13 +8007,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -7610,7 +8070,11 @@
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr"/>
-      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>45a27c1ce9114707bdf798b51110a4e7</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>9425dbb473dec25638830a11</t>
@@ -7631,7 +8095,11 @@
       <c r="AL38" s="2" t="inlineStr"/>
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr"/>
-      <c r="AO38" s="2" t="inlineStr"/>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP38" s="2" t="inlineStr"/>
       <c r="AQ38" s="2" t="inlineStr"/>
       <c r="AR38" s="2" t="inlineStr"/>
@@ -7677,8 +8145,16 @@
       <c r="BH38" s="2" t="inlineStr"/>
       <c r="BI38" s="2" t="inlineStr"/>
       <c r="BJ38" s="2" t="inlineStr"/>
-      <c r="BK38" s="2" t="inlineStr"/>
-      <c r="BL38" s="2" t="inlineStr"/>
+      <c r="BK38" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -8129,13 +8605,17 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -8188,7 +8668,11 @@
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr"/>
-      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>12807be84ac742c0a6299a99f8bac0e1</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
           <t>f44cdbd465f980b1d85b2358</t>
@@ -8209,7 +8693,11 @@
       <c r="AL41" s="2" t="inlineStr"/>
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr"/>
-      <c r="AO41" s="2" t="inlineStr"/>
+      <c r="AO41" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP41" s="2" t="inlineStr"/>
       <c r="AQ41" s="2" t="inlineStr"/>
       <c r="AR41" s="2" t="inlineStr"/>
@@ -8255,8 +8743,16 @@
       <c r="BH41" s="2" t="inlineStr"/>
       <c r="BI41" s="2" t="inlineStr"/>
       <c r="BJ41" s="2" t="inlineStr"/>
-      <c r="BK41" s="2" t="inlineStr"/>
-      <c r="BL41" s="2" t="inlineStr"/>
+      <c r="BK41" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8292,28 +8788,32 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -8357,7 +8857,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -8366,7 +8866,11 @@
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr"/>
-      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>9cc622b92c7d4415aa9c05163c383b2e</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
           <t>918c12921846b971d2279e2e</t>
@@ -8387,7 +8891,11 @@
       <c r="AL42" s="2" t="inlineStr"/>
       <c r="AM42" s="2" t="inlineStr"/>
       <c r="AN42" s="2" t="inlineStr"/>
-      <c r="AO42" s="2" t="inlineStr"/>
+      <c r="AO42" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP42" s="2" t="inlineStr"/>
       <c r="AQ42" s="2" t="inlineStr"/>
       <c r="AR42" s="2" t="inlineStr"/>
@@ -8431,10 +8939,22 @@
         </is>
       </c>
       <c r="BH42" s="2" t="inlineStr"/>
-      <c r="BI42" s="2" t="inlineStr"/>
+      <c r="BI42" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ42" s="2" t="inlineStr"/>
-      <c r="BK42" s="2" t="inlineStr"/>
-      <c r="BL42" s="2" t="inlineStr"/>
+      <c r="BK42" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8862,28 +9382,32 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -8927,7 +9451,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -8936,7 +9460,11 @@
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr"/>
-      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>b36eec21cdc74e5689518b1810e49110</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
           <t>9c61dfc4519eaf4489d835c6</t>
@@ -8957,7 +9485,11 @@
       <c r="AL45" s="2" t="inlineStr"/>
       <c r="AM45" s="2" t="inlineStr"/>
       <c r="AN45" s="2" t="inlineStr"/>
-      <c r="AO45" s="2" t="inlineStr"/>
+      <c r="AO45" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP45" s="2" t="inlineStr"/>
       <c r="AQ45" s="2" t="inlineStr"/>
       <c r="AR45" s="2" t="inlineStr"/>
@@ -9001,10 +9533,22 @@
         </is>
       </c>
       <c r="BH45" s="2" t="inlineStr"/>
-      <c r="BI45" s="2" t="inlineStr"/>
+      <c r="BI45" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ45" s="2" t="inlineStr"/>
-      <c r="BK45" s="2" t="inlineStr"/>
-      <c r="BL45" s="2" t="inlineStr"/>
+      <c r="BK45" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9040,28 +9584,32 @@
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -9105,7 +9653,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -9114,7 +9662,11 @@
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr"/>
-      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>de06c88ee5aa4bd7bbd193faac2f809b</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
           <t>e008a6e422f79bc30250bfbe</t>
@@ -9135,7 +9687,11 @@
       <c r="AL46" s="2" t="inlineStr"/>
       <c r="AM46" s="2" t="inlineStr"/>
       <c r="AN46" s="2" t="inlineStr"/>
-      <c r="AO46" s="2" t="inlineStr"/>
+      <c r="AO46" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP46" s="2" t="inlineStr"/>
       <c r="AQ46" s="2" t="inlineStr"/>
       <c r="AR46" s="2" t="inlineStr"/>
@@ -9179,10 +9735,22 @@
         </is>
       </c>
       <c r="BH46" s="2" t="inlineStr"/>
-      <c r="BI46" s="2" t="inlineStr"/>
+      <c r="BI46" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ46" s="2" t="inlineStr"/>
-      <c r="BK46" s="2" t="inlineStr"/>
-      <c r="BL46" s="2" t="inlineStr"/>
+      <c r="BK46" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9218,28 +9786,32 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -9283,7 +9855,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -9292,7 +9864,11 @@
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr"/>
-      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>fa940d70892a45d680853bef80f44898</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
           <t>a63ecfcae1fa4e09392173d7</t>
@@ -9313,7 +9889,11 @@
       <c r="AL47" s="2" t="inlineStr"/>
       <c r="AM47" s="2" t="inlineStr"/>
       <c r="AN47" s="2" t="inlineStr"/>
-      <c r="AO47" s="2" t="inlineStr"/>
+      <c r="AO47" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP47" s="2" t="inlineStr"/>
       <c r="AQ47" s="2" t="inlineStr"/>
       <c r="AR47" s="2" t="inlineStr"/>
@@ -9357,10 +9937,22 @@
         </is>
       </c>
       <c r="BH47" s="2" t="inlineStr"/>
-      <c r="BI47" s="2" t="inlineStr"/>
+      <c r="BI47" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ47" s="2" t="inlineStr"/>
-      <c r="BK47" s="2" t="inlineStr"/>
-      <c r="BL47" s="2" t="inlineStr"/>
+      <c r="BK47" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9396,28 +9988,32 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -9461,7 +10057,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -9470,7 +10066,11 @@
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr"/>
-      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>2fa1ad408da64ee7bc6cbc730c8e8a44</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
           <t>f8171b1f4173f5ebe181fe38</t>
@@ -9491,7 +10091,11 @@
       <c r="AL48" s="2" t="inlineStr"/>
       <c r="AM48" s="2" t="inlineStr"/>
       <c r="AN48" s="2" t="inlineStr"/>
-      <c r="AO48" s="2" t="inlineStr"/>
+      <c r="AO48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP48" s="2" t="inlineStr"/>
       <c r="AQ48" s="2" t="inlineStr"/>
       <c r="AR48" s="2" t="inlineStr"/>
@@ -9527,10 +10131,22 @@
         </is>
       </c>
       <c r="BH48" s="2" t="inlineStr"/>
-      <c r="BI48" s="2" t="inlineStr"/>
+      <c r="BI48" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ48" s="2" t="inlineStr"/>
-      <c r="BK48" s="2" t="inlineStr"/>
-      <c r="BL48" s="2" t="inlineStr"/>
+      <c r="BK48" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9775,13 +10391,17 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -9834,7 +10454,11 @@
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr"/>
-      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>48f66fbaa561495699e02fdf9a3ea32b</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
           <t>8655811bd9eac80d5ab80e6a</t>
@@ -9855,7 +10479,11 @@
       <c r="AL50" s="2" t="inlineStr"/>
       <c r="AM50" s="2" t="inlineStr"/>
       <c r="AN50" s="2" t="inlineStr"/>
-      <c r="AO50" s="2" t="inlineStr"/>
+      <c r="AO50" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP50" s="2" t="inlineStr"/>
       <c r="AQ50" s="2" t="inlineStr"/>
       <c r="AR50" s="2" t="inlineStr"/>
@@ -9901,8 +10529,16 @@
       <c r="BH50" s="2" t="inlineStr"/>
       <c r="BI50" s="2" t="inlineStr"/>
       <c r="BJ50" s="2" t="inlineStr"/>
-      <c r="BK50" s="2" t="inlineStr"/>
-      <c r="BL50" s="2" t="inlineStr"/>
+      <c r="BK50" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9938,28 +10574,32 @@
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -10003,7 +10643,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -10012,7 +10652,11 @@
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr"/>
-      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>26768a30458a4f25bfc9a950fee84310</t>
+        </is>
+      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
           <t>1a93f78d323a1c5f1d28570b</t>
@@ -10033,7 +10677,11 @@
       <c r="AL51" s="2" t="inlineStr"/>
       <c r="AM51" s="2" t="inlineStr"/>
       <c r="AN51" s="2" t="inlineStr"/>
-      <c r="AO51" s="2" t="inlineStr"/>
+      <c r="AO51" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP51" s="2" t="inlineStr"/>
       <c r="AQ51" s="2" t="inlineStr"/>
       <c r="AR51" s="2" t="inlineStr"/>
@@ -10077,10 +10725,22 @@
         </is>
       </c>
       <c r="BH51" s="2" t="inlineStr"/>
-      <c r="BI51" s="2" t="inlineStr"/>
+      <c r="BI51" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ51" s="2" t="inlineStr"/>
-      <c r="BK51" s="2" t="inlineStr"/>
-      <c r="BL51" s="2" t="inlineStr"/>
+      <c r="BK51" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10116,28 +10776,32 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -10181,7 +10845,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -10190,7 +10854,11 @@
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr"/>
-      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>88125b3651a64b079d92c51a04bc4bc9</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
           <t>5a3a68e2dd1fa325d2d2f7ae</t>
@@ -10211,7 +10879,11 @@
       <c r="AL52" s="2" t="inlineStr"/>
       <c r="AM52" s="2" t="inlineStr"/>
       <c r="AN52" s="2" t="inlineStr"/>
-      <c r="AO52" s="2" t="inlineStr"/>
+      <c r="AO52" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP52" s="2" t="inlineStr"/>
       <c r="AQ52" s="2" t="inlineStr"/>
       <c r="AR52" s="2" t="inlineStr"/>
@@ -10255,10 +10927,22 @@
         </is>
       </c>
       <c r="BH52" s="2" t="inlineStr"/>
-      <c r="BI52" s="2" t="inlineStr"/>
+      <c r="BI52" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ52" s="2" t="inlineStr"/>
-      <c r="BK52" s="2" t="inlineStr"/>
-      <c r="BL52" s="2" t="inlineStr"/>
+      <c r="BK52" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10294,28 +10978,32 @@
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -10359,7 +11047,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -10368,7 +11056,11 @@
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr"/>
-      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>b37d1eb22d0f485e8c506d368b64b68f</t>
+        </is>
+      </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
           <t>38df5693de9f6832a959d0dd</t>
@@ -10389,7 +11081,11 @@
       <c r="AL53" s="2" t="inlineStr"/>
       <c r="AM53" s="2" t="inlineStr"/>
       <c r="AN53" s="2" t="inlineStr"/>
-      <c r="AO53" s="2" t="inlineStr"/>
+      <c r="AO53" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP53" s="2" t="inlineStr"/>
       <c r="AQ53" s="2" t="inlineStr"/>
       <c r="AR53" s="2" t="inlineStr"/>
@@ -10433,10 +11129,22 @@
         </is>
       </c>
       <c r="BH53" s="2" t="inlineStr"/>
-      <c r="BI53" s="2" t="inlineStr"/>
+      <c r="BI53" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ53" s="2" t="inlineStr"/>
-      <c r="BK53" s="2" t="inlineStr"/>
-      <c r="BL53" s="2" t="inlineStr"/>
+      <c r="BK53" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10472,28 +11180,32 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -10537,7 +11249,7 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -10546,7 +11258,11 @@
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr"/>
-      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>93b4d4499fb94f77a83f188507112e94</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>d3a46bd45fc685662805ffc9</t>
@@ -10567,7 +11283,11 @@
       <c r="AL54" s="2" t="inlineStr"/>
       <c r="AM54" s="2" t="inlineStr"/>
       <c r="AN54" s="2" t="inlineStr"/>
-      <c r="AO54" s="2" t="inlineStr"/>
+      <c r="AO54" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP54" s="2" t="inlineStr"/>
       <c r="AQ54" s="2" t="inlineStr"/>
       <c r="AR54" s="2" t="inlineStr"/>
@@ -10611,10 +11331,22 @@
         </is>
       </c>
       <c r="BH54" s="2" t="inlineStr"/>
-      <c r="BI54" s="2" t="inlineStr"/>
+      <c r="BI54" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ54" s="2" t="inlineStr"/>
-      <c r="BK54" s="2" t="inlineStr"/>
-      <c r="BL54" s="2" t="inlineStr"/>
+      <c r="BK54" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -12258,28 +12990,32 @@
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -12323,7 +13059,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -12332,7 +13068,11 @@
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr"/>
-      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>97e3ababdb4243048a1bc82b6f15d650</t>
+        </is>
+      </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
           <t>3ccbf96aa2941a15b2bdb78e</t>
@@ -12353,7 +13093,11 @@
       <c r="AL63" s="2" t="inlineStr"/>
       <c r="AM63" s="2" t="inlineStr"/>
       <c r="AN63" s="2" t="inlineStr"/>
-      <c r="AO63" s="2" t="inlineStr"/>
+      <c r="AO63" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP63" s="2" t="inlineStr"/>
       <c r="AQ63" s="2" t="inlineStr"/>
       <c r="AR63" s="2" t="inlineStr"/>
@@ -12389,10 +13133,22 @@
         </is>
       </c>
       <c r="BH63" s="2" t="inlineStr"/>
-      <c r="BI63" s="2" t="inlineStr"/>
+      <c r="BI63" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ63" s="2" t="inlineStr"/>
-      <c r="BK63" s="2" t="inlineStr"/>
-      <c r="BL63" s="2" t="inlineStr"/>
+      <c r="BK63" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12428,28 +13184,32 @@
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -12493,7 +13253,7 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -12502,7 +13262,11 @@
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr"/>
-      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>3c4c393729ca47b395f23b204c1df09e</t>
+        </is>
+      </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
           <t>3fad7de9d9d99e999afcb1d1</t>
@@ -12523,7 +13287,11 @@
       <c r="AL64" s="2" t="inlineStr"/>
       <c r="AM64" s="2" t="inlineStr"/>
       <c r="AN64" s="2" t="inlineStr"/>
-      <c r="AO64" s="2" t="inlineStr"/>
+      <c r="AO64" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP64" s="2" t="inlineStr"/>
       <c r="AQ64" s="2" t="inlineStr"/>
       <c r="AR64" s="2" t="inlineStr"/>
@@ -12567,10 +13335,22 @@
         </is>
       </c>
       <c r="BH64" s="2" t="inlineStr"/>
-      <c r="BI64" s="2" t="inlineStr"/>
+      <c r="BI64" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ64" s="2" t="inlineStr"/>
-      <c r="BK64" s="2" t="inlineStr"/>
-      <c r="BL64" s="2" t="inlineStr"/>
+      <c r="BK64" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12606,28 +13386,32 @@
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -12671,7 +13455,7 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -12680,7 +13464,11 @@
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr"/>
-      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>e6e121628d2f489e85aeb7c43afc5d63</t>
+        </is>
+      </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
           <t>2ff309ade82c8df44a026099</t>
@@ -12701,7 +13489,11 @@
       <c r="AL65" s="2" t="inlineStr"/>
       <c r="AM65" s="2" t="inlineStr"/>
       <c r="AN65" s="2" t="inlineStr"/>
-      <c r="AO65" s="2" t="inlineStr"/>
+      <c r="AO65" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP65" s="2" t="inlineStr"/>
       <c r="AQ65" s="2" t="inlineStr"/>
       <c r="AR65" s="2" t="inlineStr"/>
@@ -12745,10 +13537,22 @@
         </is>
       </c>
       <c r="BH65" s="2" t="inlineStr"/>
-      <c r="BI65" s="2" t="inlineStr"/>
+      <c r="BI65" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ65" s="2" t="inlineStr"/>
-      <c r="BK65" s="2" t="inlineStr"/>
-      <c r="BL65" s="2" t="inlineStr"/>
+      <c r="BK65" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -13750,28 +14554,32 @@
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -13815,7 +14623,7 @@
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -13824,7 +14632,11 @@
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr"/>
-      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>597fe77d835c4ac7b55d0a01eb2ed037</t>
+        </is>
+      </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
           <t>cef255bad84d3443b44514d8</t>
@@ -13845,7 +14657,11 @@
       <c r="AL71" s="2" t="inlineStr"/>
       <c r="AM71" s="2" t="inlineStr"/>
       <c r="AN71" s="2" t="inlineStr"/>
-      <c r="AO71" s="2" t="inlineStr"/>
+      <c r="AO71" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP71" s="2" t="inlineStr"/>
       <c r="AQ71" s="2" t="inlineStr"/>
       <c r="AR71" s="2" t="inlineStr"/>
@@ -13889,10 +14705,22 @@
         </is>
       </c>
       <c r="BH71" s="2" t="inlineStr"/>
-      <c r="BI71" s="2" t="inlineStr"/>
+      <c r="BI71" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ71" s="2" t="inlineStr"/>
-      <c r="BK71" s="2" t="inlineStr"/>
-      <c r="BL71" s="2" t="inlineStr"/>
+      <c r="BK71" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -20554,28 +21382,32 @@
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -20619,7 +21451,7 @@
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -20632,7 +21464,11 @@
           <t>50100008</t>
         </is>
       </c>
-      <c r="AB105" s="2" t="inlineStr"/>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>1111aa57a12447caa6cb65f83d142653</t>
+        </is>
+      </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
           <t>3f936e2b058381b39d224912</t>
@@ -20653,7 +21489,11 @@
       <c r="AL105" s="2" t="inlineStr"/>
       <c r="AM105" s="2" t="inlineStr"/>
       <c r="AN105" s="2" t="inlineStr"/>
-      <c r="AO105" s="2" t="inlineStr"/>
+      <c r="AO105" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP105" s="2" t="inlineStr"/>
       <c r="AQ105" s="2" t="inlineStr"/>
       <c r="AR105" s="2" t="inlineStr"/>
@@ -20697,10 +21537,22 @@
         </is>
       </c>
       <c r="BH105" s="2" t="inlineStr"/>
-      <c r="BI105" s="2" t="inlineStr"/>
+      <c r="BI105" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ105" s="2" t="inlineStr"/>
-      <c r="BK105" s="2" t="inlineStr"/>
-      <c r="BL105" s="2" t="inlineStr"/>
+      <c r="BK105" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -20942,28 +21794,32 @@
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -21007,7 +21863,7 @@
       </c>
       <c r="Y107" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z107" s="2" t="inlineStr">
@@ -21020,7 +21876,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB107" s="2" t="inlineStr"/>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>2d72fde5921d4a5982b589d9b7c33953</t>
+        </is>
+      </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
           <t>e62bdd3cfb65e3fe27314d4e</t>
@@ -21041,7 +21901,11 @@
       <c r="AL107" s="2" t="inlineStr"/>
       <c r="AM107" s="2" t="inlineStr"/>
       <c r="AN107" s="2" t="inlineStr"/>
-      <c r="AO107" s="2" t="inlineStr"/>
+      <c r="AO107" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP107" s="2" t="inlineStr"/>
       <c r="AQ107" s="2" t="inlineStr"/>
       <c r="AR107" s="2" t="inlineStr"/>
@@ -21085,10 +21949,22 @@
         </is>
       </c>
       <c r="BH107" s="2" t="inlineStr"/>
-      <c r="BI107" s="2" t="inlineStr"/>
+      <c r="BI107" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ107" s="2" t="inlineStr"/>
-      <c r="BK107" s="2" t="inlineStr"/>
-      <c r="BL107" s="2" t="inlineStr"/>
+      <c r="BK107" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -21124,28 +22000,32 @@
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -21189,7 +22069,7 @@
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr">
@@ -21202,7 +22082,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB108" s="2" t="inlineStr"/>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>b1ca04dd02164232b50de3b9aac11a92</t>
+        </is>
+      </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
           <t>171bd6ed1d3e9e141a9c32b1</t>
@@ -21223,7 +22107,11 @@
       <c r="AL108" s="2" t="inlineStr"/>
       <c r="AM108" s="2" t="inlineStr"/>
       <c r="AN108" s="2" t="inlineStr"/>
-      <c r="AO108" s="2" t="inlineStr"/>
+      <c r="AO108" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP108" s="2" t="inlineStr"/>
       <c r="AQ108" s="2" t="inlineStr"/>
       <c r="AR108" s="2" t="inlineStr"/>
@@ -21259,10 +22147,22 @@
         </is>
       </c>
       <c r="BH108" s="2" t="inlineStr"/>
-      <c r="BI108" s="2" t="inlineStr"/>
+      <c r="BI108" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ108" s="2" t="inlineStr"/>
-      <c r="BK108" s="2" t="inlineStr"/>
-      <c r="BL108" s="2" t="inlineStr"/>
+      <c r="BK108" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -21915,13 +22815,17 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -21978,7 +22882,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB112" s="2" t="inlineStr"/>
+      <c r="AB112" s="2" t="inlineStr">
+        <is>
+          <t>219b7c9c8e3c42eeac0d09fdfd769d6c</t>
+        </is>
+      </c>
       <c r="AC112" s="2" t="inlineStr">
         <is>
           <t>a7e8c6f296bea60c4f45814d</t>
@@ -21999,7 +22907,11 @@
       <c r="AL112" s="2" t="inlineStr"/>
       <c r="AM112" s="2" t="inlineStr"/>
       <c r="AN112" s="2" t="inlineStr"/>
-      <c r="AO112" s="2" t="inlineStr"/>
+      <c r="AO112" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP112" s="2" t="inlineStr"/>
       <c r="AQ112" s="2" t="inlineStr"/>
       <c r="AR112" s="2" t="inlineStr"/>
@@ -22045,8 +22957,16 @@
       <c r="BH112" s="2" t="inlineStr"/>
       <c r="BI112" s="2" t="inlineStr"/>
       <c r="BJ112" s="2" t="inlineStr"/>
-      <c r="BK112" s="2" t="inlineStr"/>
-      <c r="BL112" s="2" t="inlineStr"/>
+      <c r="BK112" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -22692,28 +23612,32 @@
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -22757,7 +23681,7 @@
       </c>
       <c r="Y116" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z116" s="2" t="inlineStr">
@@ -22770,7 +23694,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB116" s="2" t="inlineStr"/>
+      <c r="AB116" s="2" t="inlineStr">
+        <is>
+          <t>5f685452f2454741b51be64db8e16c35</t>
+        </is>
+      </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
           <t>5e792a06a43b05659aff4924</t>
@@ -22791,7 +23719,11 @@
       <c r="AL116" s="2" t="inlineStr"/>
       <c r="AM116" s="2" t="inlineStr"/>
       <c r="AN116" s="2" t="inlineStr"/>
-      <c r="AO116" s="2" t="inlineStr"/>
+      <c r="AO116" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP116" s="2" t="inlineStr"/>
       <c r="AQ116" s="2" t="inlineStr"/>
       <c r="AR116" s="2" t="inlineStr"/>
@@ -22835,10 +23767,22 @@
         </is>
       </c>
       <c r="BH116" s="2" t="inlineStr"/>
-      <c r="BI116" s="2" t="inlineStr"/>
+      <c r="BI116" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ116" s="2" t="inlineStr"/>
-      <c r="BK116" s="2" t="inlineStr"/>
-      <c r="BL116" s="2" t="inlineStr"/>
+      <c r="BK116" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -23484,28 +24428,32 @@
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -23549,7 +24497,7 @@
       </c>
       <c r="Y120" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z120" s="2" t="inlineStr">
@@ -23562,7 +24510,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB120" s="2" t="inlineStr"/>
+      <c r="AB120" s="2" t="inlineStr">
+        <is>
+          <t>e8ea5965012740e19e8233a19694fd68</t>
+        </is>
+      </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
           <t>51d9814e72bfab6f3485d22c</t>
@@ -23583,7 +24535,11 @@
       <c r="AL120" s="2" t="inlineStr"/>
       <c r="AM120" s="2" t="inlineStr"/>
       <c r="AN120" s="2" t="inlineStr"/>
-      <c r="AO120" s="2" t="inlineStr"/>
+      <c r="AO120" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP120" s="2" t="inlineStr"/>
       <c r="AQ120" s="2" t="inlineStr"/>
       <c r="AR120" s="2" t="inlineStr"/>
@@ -23627,10 +24583,22 @@
         </is>
       </c>
       <c r="BH120" s="2" t="inlineStr"/>
-      <c r="BI120" s="2" t="inlineStr"/>
+      <c r="BI120" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ120" s="2" t="inlineStr"/>
-      <c r="BK120" s="2" t="inlineStr"/>
-      <c r="BL120" s="2" t="inlineStr"/>
+      <c r="BK120" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -23872,28 +24840,32 @@
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -23937,7 +24909,7 @@
       </c>
       <c r="Y122" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z122" s="2" t="inlineStr">
@@ -23950,7 +24922,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB122" s="2" t="inlineStr"/>
+      <c r="AB122" s="2" t="inlineStr">
+        <is>
+          <t>64ea87b624e04cbb8dc98b1e0f9ed2ae</t>
+        </is>
+      </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
           <t>c6a2715ac429a9a5772a3bcb</t>
@@ -23971,7 +24947,11 @@
       <c r="AL122" s="2" t="inlineStr"/>
       <c r="AM122" s="2" t="inlineStr"/>
       <c r="AN122" s="2" t="inlineStr"/>
-      <c r="AO122" s="2" t="inlineStr"/>
+      <c r="AO122" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP122" s="2" t="inlineStr"/>
       <c r="AQ122" s="2" t="inlineStr"/>
       <c r="AR122" s="2" t="inlineStr"/>
@@ -24015,10 +24995,22 @@
         </is>
       </c>
       <c r="BH122" s="2" t="inlineStr"/>
-      <c r="BI122" s="2" t="inlineStr"/>
+      <c r="BI122" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ122" s="2" t="inlineStr"/>
-      <c r="BK122" s="2" t="inlineStr"/>
-      <c r="BL122" s="2" t="inlineStr"/>
+      <c r="BK122" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -24672,28 +25664,32 @@
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -24737,7 +25733,7 @@
       </c>
       <c r="Y126" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z126" s="2" t="inlineStr">
@@ -24750,7 +25746,11 @@
           <t>163090500</t>
         </is>
       </c>
-      <c r="AB126" s="2" t="inlineStr"/>
+      <c r="AB126" s="2" t="inlineStr">
+        <is>
+          <t>b82e606feaeb4979954c08a3b6f48694</t>
+        </is>
+      </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
           <t>e7b0f63a3d3ed8530e9cec46</t>
@@ -24771,7 +25771,11 @@
       <c r="AL126" s="2" t="inlineStr"/>
       <c r="AM126" s="2" t="inlineStr"/>
       <c r="AN126" s="2" t="inlineStr"/>
-      <c r="AO126" s="2" t="inlineStr"/>
+      <c r="AO126" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP126" s="2" t="inlineStr"/>
       <c r="AQ126" s="2" t="inlineStr"/>
       <c r="AR126" s="2" t="inlineStr"/>
@@ -24815,10 +25819,22 @@
         </is>
       </c>
       <c r="BH126" s="2" t="inlineStr"/>
-      <c r="BI126" s="2" t="inlineStr"/>
+      <c r="BI126" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ126" s="2" t="inlineStr"/>
-      <c r="BK126" s="2" t="inlineStr"/>
-      <c r="BL126" s="2" t="inlineStr"/>
+      <c r="BK126" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -24854,28 +25870,32 @@
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -24919,7 +25939,7 @@
       </c>
       <c r="Y127" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z127" s="2" t="inlineStr">
@@ -24932,7 +25952,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB127" s="2" t="inlineStr"/>
+      <c r="AB127" s="2" t="inlineStr">
+        <is>
+          <t>86db324b613e407aaeace55d5b643a2b</t>
+        </is>
+      </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
           <t>c984661f74a0d82007d71c65</t>
@@ -24953,7 +25977,11 @@
       <c r="AL127" s="2" t="inlineStr"/>
       <c r="AM127" s="2" t="inlineStr"/>
       <c r="AN127" s="2" t="inlineStr"/>
-      <c r="AO127" s="2" t="inlineStr"/>
+      <c r="AO127" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP127" s="2" t="inlineStr"/>
       <c r="AQ127" s="2" t="inlineStr"/>
       <c r="AR127" s="2" t="inlineStr"/>
@@ -24989,10 +26017,22 @@
         </is>
       </c>
       <c r="BH127" s="2" t="inlineStr"/>
-      <c r="BI127" s="2" t="inlineStr"/>
+      <c r="BI127" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ127" s="2" t="inlineStr"/>
-      <c r="BK127" s="2" t="inlineStr"/>
-      <c r="BL127" s="2" t="inlineStr"/>
+      <c r="BK127" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -25194,28 +26234,32 @@
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -25259,7 +26303,7 @@
       </c>
       <c r="Y129" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z129" s="2" t="inlineStr">
@@ -25272,7 +26316,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB129" s="2" t="inlineStr"/>
+      <c r="AB129" s="2" t="inlineStr">
+        <is>
+          <t>f2b813489b624a32b4e85c8ce6fb4d9c</t>
+        </is>
+      </c>
       <c r="AC129" s="2" t="inlineStr">
         <is>
           <t>9b0d5fb338e2aab507d1b8d0</t>
@@ -25293,7 +26341,11 @@
       <c r="AL129" s="2" t="inlineStr"/>
       <c r="AM129" s="2" t="inlineStr"/>
       <c r="AN129" s="2" t="inlineStr"/>
-      <c r="AO129" s="2" t="inlineStr"/>
+      <c r="AO129" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP129" s="2" t="inlineStr"/>
       <c r="AQ129" s="2" t="inlineStr"/>
       <c r="AR129" s="2" t="inlineStr"/>
@@ -25329,10 +26381,22 @@
         </is>
       </c>
       <c r="BH129" s="2" t="inlineStr"/>
-      <c r="BI129" s="2" t="inlineStr"/>
+      <c r="BI129" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ129" s="2" t="inlineStr"/>
-      <c r="BK129" s="2" t="inlineStr"/>
-      <c r="BL129" s="2" t="inlineStr"/>
+      <c r="BK129" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -25368,28 +26432,32 @@
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L130" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -25433,7 +26501,7 @@
       </c>
       <c r="Y130" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z130" s="2" t="inlineStr">
@@ -25446,7 +26514,11 @@
           <t>38700750</t>
         </is>
       </c>
-      <c r="AB130" s="2" t="inlineStr"/>
+      <c r="AB130" s="2" t="inlineStr">
+        <is>
+          <t>eb1edc5efa6c459da0d1dd41c595ee4d</t>
+        </is>
+      </c>
       <c r="AC130" s="2" t="inlineStr">
         <is>
           <t>93da4af943b76fe2f20aec20</t>
@@ -25467,7 +26539,11 @@
       <c r="AL130" s="2" t="inlineStr"/>
       <c r="AM130" s="2" t="inlineStr"/>
       <c r="AN130" s="2" t="inlineStr"/>
-      <c r="AO130" s="2" t="inlineStr"/>
+      <c r="AO130" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP130" s="2" t="inlineStr"/>
       <c r="AQ130" s="2" t="inlineStr"/>
       <c r="AR130" s="2" t="inlineStr"/>
@@ -25503,10 +26579,22 @@
         </is>
       </c>
       <c r="BH130" s="2" t="inlineStr"/>
-      <c r="BI130" s="2" t="inlineStr"/>
+      <c r="BI130" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ130" s="2" t="inlineStr"/>
-      <c r="BK130" s="2" t="inlineStr"/>
-      <c r="BL130" s="2" t="inlineStr"/>
+      <c r="BK130" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -25542,28 +26630,32 @@
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -25607,7 +26699,7 @@
       </c>
       <c r="Y131" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z131" s="2" t="inlineStr">
@@ -25620,7 +26712,11 @@
           <t>163090500</t>
         </is>
       </c>
-      <c r="AB131" s="2" t="inlineStr"/>
+      <c r="AB131" s="2" t="inlineStr">
+        <is>
+          <t>16b0476823a94badb8cb89fbc44fd1da</t>
+        </is>
+      </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
           <t>1f9f0599ff6cc8b84d7a494b</t>
@@ -25641,7 +26737,11 @@
       <c r="AL131" s="2" t="inlineStr"/>
       <c r="AM131" s="2" t="inlineStr"/>
       <c r="AN131" s="2" t="inlineStr"/>
-      <c r="AO131" s="2" t="inlineStr"/>
+      <c r="AO131" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP131" s="2" t="inlineStr"/>
       <c r="AQ131" s="2" t="inlineStr"/>
       <c r="AR131" s="2" t="inlineStr"/>
@@ -25685,10 +26785,22 @@
         </is>
       </c>
       <c r="BH131" s="2" t="inlineStr"/>
-      <c r="BI131" s="2" t="inlineStr"/>
+      <c r="BI131" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ131" s="2" t="inlineStr"/>
-      <c r="BK131" s="2" t="inlineStr"/>
-      <c r="BL131" s="2" t="inlineStr"/>
+      <c r="BK131" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -25724,28 +26836,32 @@
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -25789,7 +26905,7 @@
       </c>
       <c r="Y132" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z132" s="2" t="inlineStr">
@@ -25802,7 +26918,11 @@
           <t>95500380</t>
         </is>
       </c>
-      <c r="AB132" s="2" t="inlineStr"/>
+      <c r="AB132" s="2" t="inlineStr">
+        <is>
+          <t>5ea4094c30854ec890701abec2244f95</t>
+        </is>
+      </c>
       <c r="AC132" s="2" t="inlineStr">
         <is>
           <t>c495fa451aa7ff74cfc6fff9</t>
@@ -25823,7 +26943,11 @@
       <c r="AL132" s="2" t="inlineStr"/>
       <c r="AM132" s="2" t="inlineStr"/>
       <c r="AN132" s="2" t="inlineStr"/>
-      <c r="AO132" s="2" t="inlineStr"/>
+      <c r="AO132" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP132" s="2" t="inlineStr"/>
       <c r="AQ132" s="2" t="inlineStr"/>
       <c r="AR132" s="2" t="inlineStr"/>
@@ -25867,10 +26991,22 @@
         </is>
       </c>
       <c r="BH132" s="2" t="inlineStr"/>
-      <c r="BI132" s="2" t="inlineStr"/>
+      <c r="BI132" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ132" s="2" t="inlineStr"/>
-      <c r="BK132" s="2" t="inlineStr"/>
-      <c r="BL132" s="2" t="inlineStr"/>
+      <c r="BK132" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -25906,28 +27042,32 @@
       <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -25971,7 +27111,7 @@
       </c>
       <c r="Y133" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z133" s="2" t="inlineStr">
@@ -25984,7 +27124,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB133" s="2" t="inlineStr"/>
+      <c r="AB133" s="2" t="inlineStr">
+        <is>
+          <t>e78c51884cc74caa94f29f446053867a</t>
+        </is>
+      </c>
       <c r="AC133" s="2" t="inlineStr">
         <is>
           <t>da184f6cebd0f5c0e6aae233</t>
@@ -26005,7 +27149,11 @@
       <c r="AL133" s="2" t="inlineStr"/>
       <c r="AM133" s="2" t="inlineStr"/>
       <c r="AN133" s="2" t="inlineStr"/>
-      <c r="AO133" s="2" t="inlineStr"/>
+      <c r="AO133" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP133" s="2" t="inlineStr"/>
       <c r="AQ133" s="2" t="inlineStr"/>
       <c r="AR133" s="2" t="inlineStr"/>
@@ -26049,10 +27197,22 @@
         </is>
       </c>
       <c r="BH133" s="2" t="inlineStr"/>
-      <c r="BI133" s="2" t="inlineStr"/>
+      <c r="BI133" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ133" s="2" t="inlineStr"/>
-      <c r="BK133" s="2" t="inlineStr"/>
-      <c r="BL133" s="2" t="inlineStr"/>
+      <c r="BK133" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">

--- a/news_daily/2026-08-10.xlsx
+++ b/news_daily/2026-08-10.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$134</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -26035,170 +26035,194 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>COST</t>
         </is>
       </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Costco</t>
         </is>
       </c>
-      <c r="E128" s="3" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>2026-08-10T01:04:10+08:00</t>
         </is>
       </c>
-      <c r="F128" s="3" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Eleven months cost Galaxy S23 owners what the Galaxy S24 got by default</t>
         </is>
       </c>
-      <c r="G128" s="3" t="inlineStr"/>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I128" s="3" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K128" s="3" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L128" s="3" t="inlineStr"/>
-      <c r="M128" s="3" t="inlineStr">
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N128" s="3" t="inlineStr">
+      <c r="N128" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O128" s="3" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>'-0.246</t>
         </is>
       </c>
-      <c r="P128" s="3" t="inlineStr"/>
-      <c r="Q128" s="3" t="inlineStr"/>
-      <c r="R128" s="3" t="inlineStr"/>
-      <c r="S128" s="3" t="inlineStr"/>
-      <c r="T128" s="3" t="inlineStr">
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr"/>
+      <c r="R128" s="2" t="inlineStr"/>
+      <c r="S128" s="2" t="inlineStr"/>
+      <c r="T128" s="2" t="inlineStr">
         <is>
           <t>人工覆核優先</t>
         </is>
       </c>
-      <c r="U128" s="3" t="inlineStr">
+      <c r="U128" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUmNmWGFJVE5DRnZobTZXTEd1YndkbFdwYk1sMllFVmRfaDhBRWxGN1hrVlR4TnNMZGQ2eWV5OWg0cGZHbFNac1VscDB5YTQzVDRIVnpweExOYXlGaFFxa1E2bmhRVDhrQWpvUzB2OWd2enFObVNocmJ1UFNjZkNBN2g5dDlZZFpncGdBcVhwZEd2cU9KM2p4cGZqdGdDQUdQbXBROFdmbGxYMzUtRkdtYmRR?oc=5</t>
         </is>
       </c>
-      <c r="V128" s="3" t="inlineStr">
+      <c r="V128" s="2" t="inlineStr">
         <is>
           <t>PhoneArena</t>
         </is>
       </c>
-      <c r="W128" s="3" t="inlineStr">
+      <c r="W128" s="2" t="inlineStr">
         <is>
           <t>Galaxy S23 用戶在 11 個月內付出的代價相當於 Galaxy S24 預設獲得的代價</t>
         </is>
       </c>
-      <c r="X128" s="3" t="inlineStr">
+      <c r="X128" s="2" t="inlineStr">
         <is>
           <t>FINANCIAL</t>
         </is>
       </c>
-      <c r="Y128" s="3" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z128" s="3" t="inlineStr">
+      <c r="Y128" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z128" s="2" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="AA128" s="3" t="inlineStr">
+      <c r="AA128" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB128" s="3" t="inlineStr"/>
-      <c r="AC128" s="3" t="inlineStr">
+      <c r="AB128" s="2" t="inlineStr">
+        <is>
+          <t>ed1f0b07616446f6aaf1c3aecb437985</t>
+        </is>
+      </c>
+      <c r="AC128" s="2" t="inlineStr">
         <is>
           <t>9015a4c41193a1d2ea02caa7</t>
         </is>
       </c>
-      <c r="AD128" s="3" t="inlineStr">
+      <c r="AD128" s="2" t="inlineStr">
         <is>
           <t>186edc11e6e2733c1b392fa0</t>
         </is>
       </c>
-      <c r="AE128" s="3" t="inlineStr"/>
-      <c r="AF128" s="3" t="inlineStr"/>
-      <c r="AG128" s="3" t="inlineStr"/>
-      <c r="AH128" s="3" t="inlineStr"/>
-      <c r="AI128" s="3" t="inlineStr"/>
-      <c r="AJ128" s="3" t="inlineStr"/>
-      <c r="AK128" s="3" t="inlineStr"/>
-      <c r="AL128" s="3" t="inlineStr"/>
-      <c r="AM128" s="3" t="inlineStr"/>
-      <c r="AN128" s="3" t="inlineStr"/>
-      <c r="AO128" s="3" t="inlineStr"/>
-      <c r="AP128" s="3" t="inlineStr"/>
-      <c r="AQ128" s="3" t="inlineStr"/>
-      <c r="AR128" s="3" t="inlineStr"/>
-      <c r="AS128" s="3" t="inlineStr"/>
-      <c r="AT128" s="3" t="inlineStr"/>
-      <c r="AU128" s="3" t="inlineStr"/>
-      <c r="AV128" s="3" t="inlineStr"/>
-      <c r="AW128" s="3" t="inlineStr"/>
-      <c r="AX128" s="3" t="inlineStr"/>
-      <c r="AY128" s="3" t="inlineStr"/>
-      <c r="AZ128" s="3" t="inlineStr"/>
-      <c r="BA128" s="3" t="inlineStr"/>
-      <c r="BB128" s="3" t="inlineStr"/>
-      <c r="BC128" s="3" t="inlineStr">
+      <c r="AE128" s="2" t="inlineStr"/>
+      <c r="AF128" s="2" t="inlineStr"/>
+      <c r="AG128" s="2" t="inlineStr"/>
+      <c r="AH128" s="2" t="inlineStr"/>
+      <c r="AI128" s="2" t="inlineStr"/>
+      <c r="AJ128" s="2" t="inlineStr"/>
+      <c r="AK128" s="2" t="inlineStr"/>
+      <c r="AL128" s="2" t="inlineStr"/>
+      <c r="AM128" s="2" t="inlineStr"/>
+      <c r="AN128" s="2" t="inlineStr"/>
+      <c r="AO128" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP128" s="2" t="inlineStr"/>
+      <c r="AQ128" s="2" t="inlineStr"/>
+      <c r="AR128" s="2" t="inlineStr"/>
+      <c r="AS128" s="2" t="inlineStr"/>
+      <c r="AT128" s="2" t="inlineStr"/>
+      <c r="AU128" s="2" t="inlineStr"/>
+      <c r="AV128" s="2" t="inlineStr"/>
+      <c r="AW128" s="2" t="inlineStr"/>
+      <c r="AX128" s="2" t="inlineStr"/>
+      <c r="AY128" s="2" t="inlineStr"/>
+      <c r="AZ128" s="2" t="inlineStr"/>
+      <c r="BA128" s="2" t="inlineStr"/>
+      <c r="BB128" s="2" t="inlineStr"/>
+      <c r="BC128" s="2" t="inlineStr">
         <is>
           <t>人工確認</t>
         </is>
       </c>
-      <c r="BD128" s="3" t="inlineStr"/>
-      <c r="BE128" s="3" t="inlineStr"/>
-      <c r="BF128" s="3" t="inlineStr"/>
-      <c r="BG128" s="3" t="inlineStr"/>
-      <c r="BH128" s="3" t="inlineStr">
+      <c r="BD128" s="2" t="inlineStr"/>
+      <c r="BE128" s="2" t="inlineStr"/>
+      <c r="BF128" s="2" t="inlineStr"/>
+      <c r="BG128" s="2" t="inlineStr"/>
+      <c r="BH128" s="2" t="inlineStr">
         <is>
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
-      <c r="BI128" s="3" t="inlineStr"/>
-      <c r="BJ128" s="3" t="inlineStr"/>
-      <c r="BK128" s="3" t="inlineStr"/>
-      <c r="BL128" s="3" t="inlineStr"/>
+      <c r="BI128" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ128" s="2" t="inlineStr"/>
+      <c r="BK128" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -27428,7 +27452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL15"/>
+  <dimension ref="A1:BL14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -30172,375 +30196,209 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Costco</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10T01:04:10+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Eleven months cost Galaxy S23 owners what the Galaxy S24 got by default</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Regeneron Pharmaceuticals, Inc.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10T00:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Bronstein, Gewirtz &amp; Grossman LLC Urges Regeneron Pharmaceuticals, Inc. Investors to Act: Class Action Filed Alleging Investor Harm</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>'-0.246</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核優先</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUmNmWGFJVE5DRnZobTZXTEd1YndkbFdwYk1sMllFVmRfaDhBRWxGN1hrVlR4TnNMZGQ2eWV5OWg0cGZHbFNac1VscDB5YTQzVDRIVnpweExOYXlGaFFxa1E2bmhRVDhrQWpvUzB2OWd2enFObVNocmJ1UFNjZkNBN2g5dDlZZFpncGdBcVhwZEd2cU9KM2p4cGZqdGdDQUdQbXBROFdmbGxYMzUtRkdtYmRR?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>PhoneArena</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t>Galaxy S23 用戶在 11 個月內付出的代價相當於 Galaxy S24 預設獲得的代價</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA14" s="3" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>'-0.611</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgJBVV95cUxPYlRwVDJCajY0U01laTE0MXR3RGpDSk9pRGFnZ3dGTWZYQm9OYzdnSmN4SF9pWTQwZzlpMXpQTmJHdkg4U0wxRHN4SHZmSWJWVGxlZUo3N2NNRmx1cHNoVzZNQXRfTUViUmV6bmo3VEVXOXJfdXQ3WE9UZjNLVGItanp4RnJTa0JmT2pTQWczdlNtX1g4WW8xRlJVeVcwUFZkbG1ZOXZYU0VKM2trcF82M05pdHRCdjB6NzVzUVRyQlVWZjVCSkVaZF9ZYkN4RndrR08waG5QZklMdkZFOVNSWU9RVEZDbDhPNkg2SFgwb24yVEdGcDZvUGpiQ2t1Zl8yUGJhaDlzeWpSN2ItajdlaktjUWpYdXRKOV93RUJMQ2xzSW5xZ2R4WGdIRjFJYnlTM1RuSGFOUzFGSHM4YVVNTkQ2V1dNQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>lincolnjournal.com</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>Bronstein, Gewirtz &amp; Grossman LLC 敦促 Regeneron Pharmaceuticals, Inc. 投資者採取行動：提起集體訴訟，指控投資者受到傷害</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="inlineStr">
-        <is>
-          <t>9015a4c41193a1d2ea02caa7</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>186edc11e6e2733c1b392fa0</t>
-        </is>
-      </c>
-      <c r="AE14" s="3" t="inlineStr"/>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr"/>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr"/>
-      <c r="BC14" s="3" t="inlineStr">
-        <is>
-          <t>人工確認</t>
-        </is>
-      </c>
-      <c r="BD14" s="3" t="inlineStr"/>
-      <c r="BE14" s="3" t="inlineStr"/>
-      <c r="BF14" s="3" t="inlineStr"/>
-      <c r="BG14" s="3" t="inlineStr"/>
-      <c r="BH14" s="3" t="inlineStr">
-        <is>
-          <t>保留人工代號；目前新聞文字無法自動佐證</t>
-        </is>
-      </c>
-      <c r="BI14" s="3" t="inlineStr"/>
-      <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr"/>
-      <c r="BL14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>f0afe55ecad64e8a873bd7559787669a</t>
+        </is>
+      </c>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>2332b38ce0def3e3119fb8e0</t>
+        </is>
+      </c>
+      <c r="AD14" s="4" t="inlineStr">
+        <is>
+          <t>0ba4223e9b90d54e076400f3</t>
+        </is>
+      </c>
+      <c r="AE14" s="4" t="inlineStr"/>
+      <c r="AF14" s="4" t="inlineStr"/>
+      <c r="AG14" s="4" t="inlineStr"/>
+      <c r="AH14" s="4" t="inlineStr"/>
+      <c r="AI14" s="4" t="inlineStr"/>
+      <c r="AJ14" s="4" t="inlineStr"/>
+      <c r="AK14" s="4" t="inlineStr"/>
+      <c r="AL14" s="4" t="inlineStr"/>
+      <c r="AM14" s="4" t="inlineStr"/>
+      <c r="AN14" s="4" t="inlineStr"/>
+      <c r="AO14" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP14" s="4" t="inlineStr"/>
+      <c r="AQ14" s="4" t="inlineStr"/>
+      <c r="AR14" s="4" t="inlineStr"/>
+      <c r="AS14" s="4" t="inlineStr"/>
+      <c r="AT14" s="4" t="inlineStr"/>
+      <c r="AU14" s="4" t="inlineStr"/>
+      <c r="AV14" s="4" t="inlineStr"/>
+      <c r="AW14" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX14" s="4" t="inlineStr"/>
+      <c r="AY14" s="4" t="inlineStr"/>
+      <c r="AZ14" s="4" t="inlineStr"/>
+      <c r="BA14" s="4" t="inlineStr"/>
+      <c r="BB14" s="4" t="inlineStr">
         <is>
           <t>REGN</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Regeneron Pharmaceuticals, Inc.</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10T00:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Bronstein, Gewirtz &amp; Grossman LLC Urges Regeneron Pharmaceuticals, Inc. Investors to Act: Class Action Filed Alleging Investor Harm</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>'-0.611</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgJBVV95cUxPYlRwVDJCajY0U01laTE0MXR3RGpDSk9pRGFnZ3dGTWZYQm9OYzdnSmN4SF9pWTQwZzlpMXpQTmJHdkg4U0wxRHN4SHZmSWJWVGxlZUo3N2NNRmx1cHNoVzZNQXRfTUViUmV6bmo3VEVXOXJfdXQ3WE9UZjNLVGItanp4RnJTa0JmT2pTQWczdlNtX1g4WW8xRlJVeVcwUFZkbG1ZOXZYU0VKM2trcF82M05pdHRCdjB6NzVzUVRyQlVWZjVCSkVaZF9ZYkN4RndrR08waG5QZklMdkZFOVNSWU9RVEZDbDhPNkg2SFgwb24yVEdGcDZvUGpiQ2t1Zl8yUGJhaDlzeWpSN2ItajdlaktjUWpYdXRKOV93RUJMQ2xzSW5xZ2R4WGdIRjFJYnlTM1RuSGFOUzFGSHM4YVVNTkQ2V1dNQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>lincolnjournal.com</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr">
-        <is>
-          <t>Bronstein, Gewirtz &amp; Grossman LLC 敦促 Regeneron Pharmaceuticals, Inc. 投資者採取行動：提起集體訴訟，指控投資者受到傷害</t>
-        </is>
-      </c>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z15" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA15" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="4" t="inlineStr">
-        <is>
-          <t>f0afe55ecad64e8a873bd7559787669a</t>
-        </is>
-      </c>
-      <c r="AC15" s="4" t="inlineStr">
-        <is>
-          <t>2332b38ce0def3e3119fb8e0</t>
-        </is>
-      </c>
-      <c r="AD15" s="4" t="inlineStr">
-        <is>
-          <t>0ba4223e9b90d54e076400f3</t>
-        </is>
-      </c>
-      <c r="AE15" s="4" t="inlineStr"/>
-      <c r="AF15" s="4" t="inlineStr"/>
-      <c r="AG15" s="4" t="inlineStr"/>
-      <c r="AH15" s="4" t="inlineStr"/>
-      <c r="AI15" s="4" t="inlineStr"/>
-      <c r="AJ15" s="4" t="inlineStr"/>
-      <c r="AK15" s="4" t="inlineStr"/>
-      <c r="AL15" s="4" t="inlineStr"/>
-      <c r="AM15" s="4" t="inlineStr"/>
-      <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP15" s="4" t="inlineStr"/>
-      <c r="AQ15" s="4" t="inlineStr"/>
-      <c r="AR15" s="4" t="inlineStr"/>
-      <c r="AS15" s="4" t="inlineStr"/>
-      <c r="AT15" s="4" t="inlineStr"/>
-      <c r="AU15" s="4" t="inlineStr"/>
-      <c r="AV15" s="4" t="inlineStr"/>
-      <c r="AW15" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX15" s="4" t="inlineStr"/>
-      <c r="AY15" s="4" t="inlineStr"/>
-      <c r="AZ15" s="4" t="inlineStr"/>
-      <c r="BA15" s="4" t="inlineStr"/>
-      <c r="BB15" s="4" t="inlineStr">
-        <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="BC15" s="4" t="inlineStr">
+      <c r="BC14" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD15" s="4" t="inlineStr"/>
-      <c r="BE15" s="4" t="inlineStr">
+      <c r="BD14" s="4" t="inlineStr"/>
+      <c r="BE14" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF15" s="4" t="inlineStr">
+      <c r="BF14" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG15" s="4" t="inlineStr">
+      <c r="BG14" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH15" s="4" t="inlineStr"/>
-      <c r="BI15" s="4" t="inlineStr"/>
-      <c r="BJ15" s="4" t="inlineStr"/>
-      <c r="BK15" s="4" t="inlineStr">
+      <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BI14" s="4" t="inlineStr"/>
+      <c r="BJ14" s="4" t="inlineStr"/>
+      <c r="BK14" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL15" s="4" t="inlineStr">
+      <c r="BL14" s="4" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL15"/>
+  <autoFilter ref="A1:BL14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
